--- a/data/PE買入區間監看.xlsx
+++ b/data/PE買入區間監看.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,89 +442,153 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PE現</t>
+          <t>收盤</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>近四季EPS</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>PER現(自算)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>PE買入門檻(P20)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>買入價(P20×EPS)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>距買入區間%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PE5年低</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PE5年高</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>PBR現</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>最新日</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14x</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>18x</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>22x</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>26x</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>30x</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.02</v>
+        <v>51.2</v>
       </c>
       <c r="D2" t="n">
-        <v>23.86</v>
+        <v>3.84</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="F2" t="n">
-        <v>-20.3</v>
+        <v>18.28</v>
       </c>
       <c r="G2" t="n">
-        <v>19.02</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>93.56</v>
+        <v>70.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>-27</v>
       </c>
       <c r="J2" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>12.83</v>
+      </c>
+      <c r="K2" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>115.2</v>
       </c>
     </row>
     <row r="3">
@@ -539,402 +603,382 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>180</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="E3" t="n">
         <v>11.78</v>
       </c>
-      <c r="D3" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="J3" t="n">
         <v>11.19</v>
       </c>
-      <c r="H3" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="L3" t="n">
         <v>7.5</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>213.9</v>
+      </c>
+      <c r="P3" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>397.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>458.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.52</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>13.49</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="H4" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+      <c r="K4" t="n">
+        <v>85.66</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>97</v>
+      </c>
+      <c r="R4" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="S4" t="n">
+        <v>132.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.33</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>18.33</v>
+        <v>3.91</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>19.16</v>
       </c>
       <c r="F5" t="n">
-        <v>-27.3</v>
+        <v>26.7</v>
       </c>
       <c r="G5" t="n">
-        <v>12.83</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>44.21</v>
+        <v>104.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>-28.3</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+        <v>16.62</v>
+      </c>
+      <c r="K5" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>86</v>
+      </c>
+      <c r="R5" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>117.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.84</v>
+        <v>82.5</v>
       </c>
       <c r="D6" t="n">
-        <v>13.83</v>
+        <v>6.39</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>12.91</v>
       </c>
       <c r="F6" t="n">
-        <v>-28.9</v>
+        <v>13.45</v>
       </c>
       <c r="G6" t="n">
-        <v>9.08</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>33.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.23</v>
+        <v>-4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>12.04</v>
+      </c>
+      <c r="K6" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>191.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.87</v>
+        <v>1455</v>
       </c>
       <c r="D7" t="n">
-        <v>29.17</v>
+        <v>81.16</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>17.93</v>
       </c>
       <c r="F7" t="n">
-        <v>-31.9</v>
+        <v>20.78</v>
       </c>
       <c r="G7" t="n">
-        <v>18.46</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>64.16</v>
+        <v>1686.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>-13.7</v>
       </c>
       <c r="J7" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+        <v>11.54</v>
+      </c>
+      <c r="K7" t="n">
+        <v>89.78</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>811.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1136.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1460.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1785.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2110.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2434.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.8</v>
+        <v>179</v>
       </c>
       <c r="D8" t="n">
-        <v>19.62</v>
+        <v>10.62</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>16.85</v>
       </c>
       <c r="F8" t="n">
-        <v>-24.6</v>
+        <v>17.31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>199.26</v>
+        <v>183.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2.28</v>
+        <v>-2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-25.6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="H9" t="n">
-        <v>121.48</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2480</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>敦陽科</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="D10" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="H10" t="n">
-        <v>23.15</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="J10" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6690</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>安碁資訊</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="D11" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="G11" t="n">
         <v>14.26</v>
       </c>
-      <c r="H11" t="n">
-        <v>32.61</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="K8" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="L8" t="n">
         <v>5.03</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="D12" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="E12" t="n">
-        <v>11</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>17.65</v>
-      </c>
-      <c r="H12" t="n">
-        <v>54.32</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>276.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>318.6</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,89 +1008,153 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PE現</t>
+          <t>收盤</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>近四季EPS</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>PER現(自算)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>PE買入門檻(P20)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>買入價(P20×EPS)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>距買入區間%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PE5年低</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PE5年高</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>PBR現</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>最新日</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14x</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>18x</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>22x</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>26x</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>30x</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.02</v>
+        <v>51.2</v>
       </c>
       <c r="D2" t="n">
-        <v>23.86</v>
+        <v>3.84</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="F2" t="n">
-        <v>-20.3</v>
+        <v>18.28</v>
       </c>
       <c r="G2" t="n">
-        <v>19.02</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>93.56</v>
+        <v>70.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>-27</v>
       </c>
       <c r="J2" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>12.83</v>
+      </c>
+      <c r="K2" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>115.2</v>
       </c>
     </row>
     <row r="3">
@@ -1061,443 +1169,707 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>180</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="E3" t="n">
         <v>11.78</v>
       </c>
-      <c r="D3" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="J3" t="n">
         <v>11.19</v>
       </c>
-      <c r="H3" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="L3" t="n">
         <v>7.5</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>213.9</v>
+      </c>
+      <c r="P3" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>397.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>458.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.52</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>13.49</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="H4" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+      <c r="K4" t="n">
+        <v>85.66</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>97</v>
+      </c>
+      <c r="R4" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="S4" t="n">
+        <v>132.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.33</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>18.33</v>
+        <v>3.91</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>19.16</v>
       </c>
       <c r="F5" t="n">
-        <v>-27.3</v>
+        <v>26.7</v>
       </c>
       <c r="G5" t="n">
-        <v>12.83</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>44.21</v>
+        <v>104.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>-28.3</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+        <v>16.62</v>
+      </c>
+      <c r="K5" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>86</v>
+      </c>
+      <c r="R5" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>117.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.84</v>
+        <v>82.5</v>
       </c>
       <c r="D6" t="n">
-        <v>13.83</v>
+        <v>6.39</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>12.91</v>
       </c>
       <c r="F6" t="n">
-        <v>-28.9</v>
+        <v>13.45</v>
       </c>
       <c r="G6" t="n">
-        <v>9.08</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>33.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.23</v>
+        <v>-4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>12.04</v>
+      </c>
+      <c r="K6" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>191.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.87</v>
+        <v>1455</v>
       </c>
       <c r="D7" t="n">
-        <v>29.17</v>
+        <v>81.16</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>17.93</v>
       </c>
       <c r="F7" t="n">
-        <v>-31.9</v>
+        <v>20.78</v>
       </c>
       <c r="G7" t="n">
-        <v>18.46</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>64.16</v>
+        <v>1686.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>-13.7</v>
       </c>
       <c r="J7" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+        <v>11.54</v>
+      </c>
+      <c r="K7" t="n">
+        <v>89.78</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>811.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1136.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1460.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1785.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2110.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2434.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.8</v>
+        <v>179</v>
       </c>
       <c r="D8" t="n">
-        <v>19.62</v>
+        <v>10.62</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>16.85</v>
       </c>
       <c r="F8" t="n">
-        <v>-24.6</v>
+        <v>17.31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>199.26</v>
+        <v>183.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2.28</v>
+        <v>-2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+        <v>14.26</v>
+      </c>
+      <c r="K8" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>276.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>318.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.01</v>
+        <v>625</v>
       </c>
       <c r="D9" t="n">
-        <v>13.45</v>
+        <v>31.45</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>19.87</v>
       </c>
       <c r="F9" t="n">
-        <v>-25.6</v>
+        <v>18.15</v>
       </c>
       <c r="G9" t="n">
-        <v>7.61</v>
+        <v>36</v>
       </c>
       <c r="H9" t="n">
-        <v>121.48</v>
+        <v>570.7</v>
       </c>
       <c r="I9" t="n">
-        <v>2.68</v>
+        <v>9.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>14.17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>440.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>566.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>691.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>817.7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>943.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12.34</v>
+        <v>112</v>
       </c>
       <c r="D10" t="n">
-        <v>13.95</v>
+        <v>7.94</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>14.11</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>10.62</v>
+        <v>63</v>
       </c>
       <c r="H10" t="n">
-        <v>23.15</v>
+        <v>65.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.51</v>
+        <v>70.2</v>
       </c>
       <c r="J10" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>6.23</v>
+      </c>
+      <c r="K10" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>238.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16.85</v>
+        <v>793</v>
       </c>
       <c r="D11" t="n">
-        <v>19.12</v>
+        <v>40.37</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>19.64</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.9</v>
+        <v>11.13</v>
       </c>
       <c r="G11" t="n">
-        <v>14.26</v>
+        <v>68</v>
       </c>
       <c r="H11" t="n">
-        <v>32.61</v>
+        <v>449.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.83</v>
+        <v>76.5</v>
       </c>
       <c r="J11" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+        <v>4.92</v>
+      </c>
+      <c r="K11" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>403.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>565.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>726.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>888.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1049.6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1211.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.12</v>
+        <v>789</v>
       </c>
       <c r="D12" t="n">
-        <v>25.23</v>
+        <v>55.96</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>14.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.3</v>
+        <v>6.45</v>
       </c>
       <c r="G12" t="n">
-        <v>17.65</v>
+        <v>71</v>
       </c>
       <c r="H12" t="n">
-        <v>54.32</v>
+        <v>360.8</v>
       </c>
       <c r="I12" t="n">
-        <v>6.05</v>
+        <v>118.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>4.31</v>
+      </c>
+      <c r="K12" t="n">
+        <v>111.49</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>559.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>783.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1007.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1231.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1455</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1678.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.11</v>
+        <v>153.5</v>
       </c>
       <c r="D13" t="n">
-        <v>15.47</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>18.3</v>
       </c>
       <c r="F13" t="n">
-        <v>10.6</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>12.54</v>
+        <v>79</v>
       </c>
       <c r="H13" t="n">
-        <v>35.53</v>
+        <v>117.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.11</v>
+        <v>30.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>10.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>218.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>251.7</v>
       </c>
     </row>
     <row r="14">
@@ -1512,320 +1884,512 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.13</v>
+        <v>2400</v>
       </c>
       <c r="D14" t="n">
-        <v>11.66</v>
+        <v>61.06</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>39.31</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>11.68</v>
       </c>
       <c r="G14" t="n">
+        <v>84</v>
+      </c>
+      <c r="H14" t="n">
+        <v>713.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="J14" t="n">
         <v>8.91</v>
       </c>
-      <c r="H14" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
+        <v>59.89</v>
+      </c>
+      <c r="L14" t="n">
         <v>3.76</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>610.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>854.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1099.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1343.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1587.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1831.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12.22</v>
+        <v>2410</v>
       </c>
       <c r="D15" t="n">
-        <v>9.77</v>
+        <v>74.39</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>32.4</v>
       </c>
       <c r="F15" t="n">
-        <v>25.1</v>
+        <v>15.67</v>
       </c>
       <c r="G15" t="n">
-        <v>5.31</v>
+        <v>97</v>
       </c>
       <c r="H15" t="n">
-        <v>30.3</v>
+        <v>1166</v>
       </c>
       <c r="I15" t="n">
-        <v>2.02</v>
+        <v>106.7</v>
       </c>
       <c r="J15" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>12.54</v>
+      </c>
+      <c r="K15" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>743.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1041.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1339</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1636.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1934.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2231.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19.87</v>
+        <v>2150</v>
       </c>
       <c r="D16" t="n">
-        <v>18.07</v>
+        <v>27.11</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>79.31</v>
       </c>
       <c r="F16" t="n">
-        <v>9.9</v>
+        <v>24.01</v>
       </c>
       <c r="G16" t="n">
-        <v>14.28</v>
+        <v>97</v>
       </c>
       <c r="H16" t="n">
-        <v>30.5</v>
+        <v>651</v>
       </c>
       <c r="I16" t="n">
-        <v>10.42</v>
+        <v>230.3</v>
       </c>
       <c r="J16" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+        <v>20.41</v>
+      </c>
+      <c r="K16" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>704.9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>813.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11.82</v>
+        <v>2435</v>
       </c>
       <c r="D17" t="n">
-        <v>8.94</v>
+        <v>52.88</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>46.05</v>
       </c>
       <c r="F17" t="n">
-        <v>32.2</v>
+        <v>25.4</v>
       </c>
       <c r="G17" t="n">
-        <v>6.75</v>
+        <v>98</v>
       </c>
       <c r="H17" t="n">
-        <v>30.41</v>
+        <v>1343.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>81.3</v>
       </c>
       <c r="J17" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>17.64</v>
+      </c>
+      <c r="K17" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>528.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>740.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>951.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1163.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1374.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1586.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>超豐</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.2</v>
+        <v>135</v>
       </c>
       <c r="D18" t="n">
-        <v>6.43</v>
+        <v>4.67</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>28.91</v>
       </c>
       <c r="F18" t="n">
-        <v>89.7</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>4.55</v>
+        <v>99</v>
       </c>
       <c r="H18" t="n">
-        <v>111.82</v>
+        <v>45.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.15</v>
+        <v>195.5</v>
       </c>
       <c r="J18" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>5.31</v>
+      </c>
+      <c r="K18" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="P18" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>140.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.78</v>
+        <v>347.5</v>
       </c>
       <c r="D19" t="n">
-        <v>9.609999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>33.9</v>
       </c>
       <c r="F19" t="n">
-        <v>147.5</v>
+        <v>14.07</v>
       </c>
       <c r="G19" t="n">
-        <v>5.87</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>107.47</v>
+        <v>144.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>140.9</v>
       </c>
       <c r="J19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>9.109999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>307.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19.64</v>
+        <v>5600</v>
       </c>
       <c r="D20" t="n">
-        <v>11.68</v>
+        <v>46.55</v>
       </c>
       <c r="E20" t="n">
-        <v>70</v>
+        <v>120.3</v>
       </c>
       <c r="F20" t="n">
-        <v>68.09999999999999</v>
+        <v>13.29</v>
       </c>
       <c r="G20" t="n">
-        <v>4.75</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>36.89</v>
+        <v>618.9</v>
       </c>
       <c r="I20" t="n">
-        <v>18.56</v>
+        <v>804.9</v>
       </c>
       <c r="J20" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
+        <v>7.61</v>
+      </c>
+      <c r="K20" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>651.7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>837.9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1024.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1210.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1396.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50.63</v>
+        <v>561</v>
       </c>
       <c r="D21" t="n">
-        <v>20.78</v>
+        <v>5.22</v>
       </c>
       <c r="E21" t="n">
-        <v>87</v>
+        <v>107.47</v>
       </c>
       <c r="F21" t="n">
-        <v>143.7</v>
+        <v>9.59</v>
       </c>
       <c r="G21" t="n">
-        <v>11.56</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>84.63</v>
+        <v>50.1</v>
       </c>
       <c r="I21" t="n">
-        <v>13.47</v>
+        <v>1020.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+        <v>5.87</v>
+      </c>
+      <c r="K21" t="n">
+        <v>107.47</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="P21" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="S21" t="n">
+        <v>156.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/PE買入區間監看.xlsx
+++ b/data/PE買入區間監看.xlsx
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="D2" t="n">
         <v>3.84</v>
       </c>
       <c r="E2" t="n">
-        <v>13.33</v>
+        <v>13.2</v>
       </c>
       <c r="F2" t="n">
-        <v>18.28</v>
+        <v>18.26</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-27</v>
+        <v>-27.7</v>
       </c>
       <c r="J2" t="n">
         <v>12.83</v>
@@ -565,11 +565,11 @@
         <v>45.6</v>
       </c>
       <c r="L2" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>180</v>
+        <v>178.5</v>
       </c>
       <c r="D3" t="n">
         <v>15.28</v>
       </c>
       <c r="E3" t="n">
-        <v>11.78</v>
+        <v>11.68</v>
       </c>
       <c r="F3" t="n">
         <v>13.79</v>
@@ -618,10 +618,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>210.8</v>
+        <v>210.7</v>
       </c>
       <c r="I3" t="n">
-        <v>-14.6</v>
+        <v>-15.3</v>
       </c>
       <c r="J3" t="n">
         <v>11.19</v>
@@ -630,11 +630,11 @@
         <v>29.38</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -659,131 +659,131 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>74.3</v>
       </c>
       <c r="D4" t="n">
-        <v>4.41</v>
+        <v>3.91</v>
       </c>
       <c r="E4" t="n">
-        <v>14.06</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>19.09</v>
+        <v>26.68</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>84.2</v>
+        <v>104.3</v>
       </c>
       <c r="I4" t="n">
-        <v>-26.4</v>
+        <v>-28.8</v>
       </c>
       <c r="J4" t="n">
-        <v>13.49</v>
+        <v>16.62</v>
       </c>
       <c r="K4" t="n">
-        <v>85.66</v>
+        <v>61.2</v>
       </c>
       <c r="L4" t="n">
-        <v>3.31</v>
+        <v>5.06</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>44.1</v>
+        <v>39.1</v>
       </c>
       <c r="O4" t="n">
-        <v>61.7</v>
+        <v>54.7</v>
       </c>
       <c r="P4" t="n">
-        <v>79.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="R4" t="n">
-        <v>114.7</v>
+        <v>101.7</v>
       </c>
       <c r="S4" t="n">
-        <v>132.3</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>3.91</v>
+        <v>4.41</v>
       </c>
       <c r="E5" t="n">
-        <v>19.16</v>
+        <v>14.6</v>
       </c>
       <c r="F5" t="n">
-        <v>26.7</v>
+        <v>19.08</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>104.4</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-28.3</v>
+        <v>-23.5</v>
       </c>
       <c r="J5" t="n">
-        <v>16.62</v>
+        <v>13.49</v>
       </c>
       <c r="K5" t="n">
-        <v>61.2</v>
+        <v>85.66</v>
       </c>
       <c r="L5" t="n">
-        <v>5.02</v>
+        <v>3.19</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>39.1</v>
+        <v>44.1</v>
       </c>
       <c r="O5" t="n">
-        <v>54.7</v>
+        <v>61.7</v>
       </c>
       <c r="P5" t="n">
-        <v>70.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="R5" t="n">
-        <v>101.7</v>
+        <v>114.7</v>
       </c>
       <c r="S5" t="n">
-        <v>117.3</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="6">
@@ -807,7 +807,7 @@
         <v>12.91</v>
       </c>
       <c r="F6" t="n">
-        <v>13.45</v>
+        <v>13.44</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
@@ -825,11 +825,11 @@
         <v>19.29</v>
       </c>
       <c r="L6" t="n">
-        <v>6.75</v>
+        <v>6.06</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -863,25 +863,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="D7" t="n">
         <v>81.16</v>
       </c>
       <c r="E7" t="n">
-        <v>17.93</v>
+        <v>17.87</v>
       </c>
       <c r="F7" t="n">
-        <v>20.78</v>
+        <v>20.74</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>1686.5</v>
+        <v>1682.9</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.7</v>
+        <v>-13.8</v>
       </c>
       <c r="J7" t="n">
         <v>11.54</v>
@@ -890,11 +890,11 @@
         <v>89.78</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -928,25 +928,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>179</v>
+        <v>179.5</v>
       </c>
       <c r="D8" t="n">
         <v>10.62</v>
       </c>
       <c r="E8" t="n">
-        <v>16.85</v>
+        <v>16.9</v>
       </c>
       <c r="F8" t="n">
         <v>17.31</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
         <v>183.8</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="J8" t="n">
         <v>14.26</v>
@@ -955,11 +955,11 @@
         <v>31.4</v>
       </c>
       <c r="L8" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1104,25 +1104,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="D2" t="n">
         <v>3.84</v>
       </c>
       <c r="E2" t="n">
-        <v>13.33</v>
+        <v>13.2</v>
       </c>
       <c r="F2" t="n">
-        <v>18.28</v>
+        <v>18.26</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-27</v>
+        <v>-27.7</v>
       </c>
       <c r="J2" t="n">
         <v>12.83</v>
@@ -1131,11 +1131,11 @@
         <v>45.6</v>
       </c>
       <c r="L2" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>180</v>
+        <v>178.5</v>
       </c>
       <c r="D3" t="n">
         <v>15.28</v>
       </c>
       <c r="E3" t="n">
-        <v>11.78</v>
+        <v>11.68</v>
       </c>
       <c r="F3" t="n">
         <v>13.79</v>
@@ -1184,10 +1184,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>210.8</v>
+        <v>210.7</v>
       </c>
       <c r="I3" t="n">
-        <v>-14.6</v>
+        <v>-15.3</v>
       </c>
       <c r="J3" t="n">
         <v>11.19</v>
@@ -1196,11 +1196,11 @@
         <v>29.38</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -1225,131 +1225,131 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>74.3</v>
       </c>
       <c r="D4" t="n">
-        <v>4.41</v>
+        <v>3.91</v>
       </c>
       <c r="E4" t="n">
-        <v>14.06</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>19.09</v>
+        <v>26.68</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>84.2</v>
+        <v>104.3</v>
       </c>
       <c r="I4" t="n">
-        <v>-26.4</v>
+        <v>-28.8</v>
       </c>
       <c r="J4" t="n">
-        <v>13.49</v>
+        <v>16.62</v>
       </c>
       <c r="K4" t="n">
-        <v>85.66</v>
+        <v>61.2</v>
       </c>
       <c r="L4" t="n">
-        <v>3.31</v>
+        <v>5.06</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>44.1</v>
+        <v>39.1</v>
       </c>
       <c r="O4" t="n">
-        <v>61.7</v>
+        <v>54.7</v>
       </c>
       <c r="P4" t="n">
-        <v>79.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="R4" t="n">
-        <v>114.7</v>
+        <v>101.7</v>
       </c>
       <c r="S4" t="n">
-        <v>132.3</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>3.91</v>
+        <v>4.41</v>
       </c>
       <c r="E5" t="n">
-        <v>19.16</v>
+        <v>14.6</v>
       </c>
       <c r="F5" t="n">
-        <v>26.7</v>
+        <v>19.08</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>104.4</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-28.3</v>
+        <v>-23.5</v>
       </c>
       <c r="J5" t="n">
-        <v>16.62</v>
+        <v>13.49</v>
       </c>
       <c r="K5" t="n">
-        <v>61.2</v>
+        <v>85.66</v>
       </c>
       <c r="L5" t="n">
-        <v>5.02</v>
+        <v>3.19</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>39.1</v>
+        <v>44.1</v>
       </c>
       <c r="O5" t="n">
-        <v>54.7</v>
+        <v>61.7</v>
       </c>
       <c r="P5" t="n">
-        <v>70.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="R5" t="n">
-        <v>101.7</v>
+        <v>114.7</v>
       </c>
       <c r="S5" t="n">
-        <v>117.3</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="6">
@@ -1373,7 +1373,7 @@
         <v>12.91</v>
       </c>
       <c r="F6" t="n">
-        <v>13.45</v>
+        <v>13.44</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
@@ -1391,11 +1391,11 @@
         <v>19.29</v>
       </c>
       <c r="L6" t="n">
-        <v>6.75</v>
+        <v>6.06</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="D7" t="n">
         <v>81.16</v>
       </c>
       <c r="E7" t="n">
-        <v>17.93</v>
+        <v>17.87</v>
       </c>
       <c r="F7" t="n">
-        <v>20.78</v>
+        <v>20.74</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>1686.5</v>
+        <v>1682.9</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.7</v>
+        <v>-13.8</v>
       </c>
       <c r="J7" t="n">
         <v>11.54</v>
@@ -1456,11 +1456,11 @@
         <v>89.78</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1494,25 +1494,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>179</v>
+        <v>179.5</v>
       </c>
       <c r="D8" t="n">
         <v>10.62</v>
       </c>
       <c r="E8" t="n">
-        <v>16.85</v>
+        <v>16.9</v>
       </c>
       <c r="F8" t="n">
         <v>17.31</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
         <v>183.8</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="J8" t="n">
         <v>14.26</v>
@@ -1521,11 +1521,11 @@
         <v>31.4</v>
       </c>
       <c r="L8" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1559,25 +1559,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="D9" t="n">
         <v>31.45</v>
       </c>
       <c r="E9" t="n">
-        <v>19.87</v>
+        <v>20.22</v>
       </c>
       <c r="F9" t="n">
         <v>18.15</v>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H9" t="n">
-        <v>570.7</v>
+        <v>570.8</v>
       </c>
       <c r="I9" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="J9" t="n">
         <v>14.17</v>
@@ -1586,11 +1586,11 @@
         <v>31.63</v>
       </c>
       <c r="L9" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="D10" t="n">
         <v>7.94</v>
       </c>
       <c r="E10" t="n">
-        <v>14.11</v>
+        <v>14.17</v>
       </c>
       <c r="F10" t="n">
         <v>8.289999999999999</v>
@@ -1642,7 +1642,7 @@
         <v>65.8</v>
       </c>
       <c r="I10" t="n">
-        <v>70.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>6.23</v>
@@ -1651,11 +1651,11 @@
         <v>29.13</v>
       </c>
       <c r="L10" t="n">
-        <v>5.89</v>
+        <v>3.38</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1689,25 +1689,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="D11" t="n">
         <v>40.37</v>
       </c>
       <c r="E11" t="n">
-        <v>19.64</v>
+        <v>19.27</v>
       </c>
       <c r="F11" t="n">
         <v>11.13</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H11" t="n">
         <v>449.4</v>
       </c>
       <c r="I11" t="n">
-        <v>76.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>4.92</v>
@@ -1716,11 +1716,11 @@
         <v>30.21</v>
       </c>
       <c r="L11" t="n">
-        <v>4.54</v>
+        <v>4.63</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1754,13 +1754,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D12" t="n">
         <v>55.96</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1</v>
+        <v>14.08</v>
       </c>
       <c r="F12" t="n">
         <v>6.45</v>
@@ -1772,7 +1772,7 @@
         <v>360.8</v>
       </c>
       <c r="I12" t="n">
-        <v>118.7</v>
+        <v>118.4</v>
       </c>
       <c r="J12" t="n">
         <v>4.31</v>
@@ -1781,11 +1781,11 @@
         <v>111.49</v>
       </c>
       <c r="L12" t="n">
-        <v>6.3</v>
+        <v>5.33</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1819,25 +1819,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="D13" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>18.3</v>
+        <v>18.41</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H13" t="n">
         <v>117.5</v>
       </c>
       <c r="I13" t="n">
-        <v>30.7</v>
+        <v>31.5</v>
       </c>
       <c r="J13" t="n">
         <v>10.9</v>
@@ -1846,11 +1846,11 @@
         <v>23.27</v>
       </c>
       <c r="L13" t="n">
-        <v>6.03</v>
+        <v>5.05</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2400</v>
+        <v>2420</v>
       </c>
       <c r="D14" t="n">
         <v>61.06</v>
       </c>
       <c r="E14" t="n">
-        <v>39.31</v>
+        <v>39.63</v>
       </c>
       <c r="F14" t="n">
         <v>11.68</v>
@@ -1899,10 +1899,10 @@
         <v>84</v>
       </c>
       <c r="H14" t="n">
-        <v>713.2</v>
+        <v>713.4</v>
       </c>
       <c r="I14" t="n">
-        <v>236.5</v>
+        <v>239.2</v>
       </c>
       <c r="J14" t="n">
         <v>8.91</v>
@@ -1911,11 +1911,11 @@
         <v>59.89</v>
       </c>
       <c r="L14" t="n">
-        <v>3.76</v>
+        <v>0.87</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1940,261 +1940,261 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2410</v>
+        <v>2150</v>
       </c>
       <c r="D15" t="n">
-        <v>74.39</v>
+        <v>27.11</v>
       </c>
       <c r="E15" t="n">
-        <v>32.4</v>
+        <v>79.31</v>
       </c>
       <c r="F15" t="n">
-        <v>15.67</v>
+        <v>24.02</v>
       </c>
       <c r="G15" t="n">
         <v>97</v>
       </c>
       <c r="H15" t="n">
-        <v>1166</v>
+        <v>651.1</v>
       </c>
       <c r="I15" t="n">
-        <v>106.7</v>
+        <v>230.2</v>
       </c>
       <c r="J15" t="n">
-        <v>12.54</v>
+        <v>20.41</v>
       </c>
       <c r="K15" t="n">
-        <v>35.51</v>
+        <v>98.53</v>
       </c>
       <c r="L15" t="n">
-        <v>3.08</v>
+        <v>0.54</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>743.9</v>
+        <v>271.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1041.5</v>
+        <v>379.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1339</v>
+        <v>488</v>
       </c>
       <c r="Q15" t="n">
-        <v>1636.6</v>
+        <v>596.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1934.1</v>
+        <v>704.9</v>
       </c>
       <c r="S15" t="n">
-        <v>2231.7</v>
+        <v>813.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2150</v>
+        <v>2595</v>
       </c>
       <c r="D16" t="n">
-        <v>27.11</v>
+        <v>52.88</v>
       </c>
       <c r="E16" t="n">
-        <v>79.31</v>
+        <v>49.07</v>
       </c>
       <c r="F16" t="n">
-        <v>24.01</v>
+        <v>25.4</v>
       </c>
       <c r="G16" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H16" t="n">
-        <v>651</v>
+        <v>1343.4</v>
       </c>
       <c r="I16" t="n">
-        <v>230.3</v>
+        <v>93.2</v>
       </c>
       <c r="J16" t="n">
-        <v>20.41</v>
+        <v>17.64</v>
       </c>
       <c r="K16" t="n">
-        <v>98.53</v>
+        <v>56.76</v>
       </c>
       <c r="L16" t="n">
-        <v>3.68</v>
+        <v>0.58</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>271.1</v>
+        <v>528.8</v>
       </c>
       <c r="O16" t="n">
-        <v>379.5</v>
+        <v>740.3</v>
       </c>
       <c r="P16" t="n">
-        <v>488</v>
+        <v>951.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>596.4</v>
+        <v>1163.4</v>
       </c>
       <c r="R16" t="n">
-        <v>704.9</v>
+        <v>1374.9</v>
       </c>
       <c r="S16" t="n">
-        <v>813.3</v>
+        <v>1586.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2435</v>
+        <v>2510</v>
       </c>
       <c r="D17" t="n">
-        <v>52.88</v>
+        <v>74.39</v>
       </c>
       <c r="E17" t="n">
-        <v>46.05</v>
+        <v>33.74</v>
       </c>
       <c r="F17" t="n">
-        <v>25.4</v>
+        <v>15.69</v>
       </c>
       <c r="G17" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H17" t="n">
-        <v>1343.3</v>
+        <v>1167.3</v>
       </c>
       <c r="I17" t="n">
-        <v>81.3</v>
+        <v>115</v>
       </c>
       <c r="J17" t="n">
-        <v>17.64</v>
+        <v>12.54</v>
       </c>
       <c r="K17" t="n">
-        <v>56.76</v>
+        <v>35.51</v>
       </c>
       <c r="L17" t="n">
-        <v>3.13</v>
+        <v>0.88</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>528.8</v>
+        <v>743.9</v>
       </c>
       <c r="O17" t="n">
-        <v>740.3</v>
+        <v>1041.5</v>
       </c>
       <c r="P17" t="n">
-        <v>951.8</v>
+        <v>1339</v>
       </c>
       <c r="Q17" t="n">
-        <v>1163.4</v>
+        <v>1636.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1374.9</v>
+        <v>1934.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1586.4</v>
+        <v>2231.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>135</v>
+        <v>5825</v>
       </c>
       <c r="D18" t="n">
-        <v>4.67</v>
+        <v>46.55</v>
       </c>
       <c r="E18" t="n">
-        <v>28.91</v>
+        <v>125.13</v>
       </c>
       <c r="F18" t="n">
-        <v>9.779999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="G18" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>45.7</v>
+        <v>619.1</v>
       </c>
       <c r="I18" t="n">
-        <v>195.5</v>
+        <v>840.9</v>
       </c>
       <c r="J18" t="n">
-        <v>5.31</v>
+        <v>7.61</v>
       </c>
       <c r="K18" t="n">
-        <v>30.3</v>
+        <v>125.13</v>
       </c>
       <c r="L18" t="n">
-        <v>5.21</v>
+        <v>0.43</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>46.7</v>
+        <v>465.5</v>
       </c>
       <c r="O18" t="n">
-        <v>65.40000000000001</v>
+        <v>651.7</v>
       </c>
       <c r="P18" t="n">
-        <v>84.09999999999999</v>
+        <v>837.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>102.7</v>
+        <v>1024.1</v>
       </c>
       <c r="R18" t="n">
-        <v>121.4</v>
+        <v>1210.3</v>
       </c>
       <c r="S18" t="n">
-        <v>140.1</v>
+        <v>1396.5</v>
       </c>
     </row>
     <row r="19">
@@ -2209,13 +2209,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>347.5</v>
+        <v>353</v>
       </c>
       <c r="D19" t="n">
         <v>10.25</v>
       </c>
       <c r="E19" t="n">
-        <v>33.9</v>
+        <v>34.44</v>
       </c>
       <c r="F19" t="n">
         <v>14.07</v>
@@ -2224,23 +2224,23 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>144.2</v>
+        <v>144.3</v>
       </c>
       <c r="I19" t="n">
-        <v>140.9</v>
+        <v>144.7</v>
       </c>
       <c r="J19" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>33.9</v>
+        <v>34.44</v>
       </c>
       <c r="L19" t="n">
-        <v>3.91</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -2265,131 +2265,131 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5600</v>
+        <v>617</v>
       </c>
       <c r="D20" t="n">
-        <v>46.55</v>
+        <v>5.22</v>
       </c>
       <c r="E20" t="n">
-        <v>120.3</v>
+        <v>118.2</v>
       </c>
       <c r="F20" t="n">
-        <v>13.29</v>
+        <v>9.59</v>
       </c>
       <c r="G20" t="n">
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>618.9</v>
+        <v>50.1</v>
       </c>
       <c r="I20" t="n">
-        <v>804.9</v>
+        <v>1132.3</v>
       </c>
       <c r="J20" t="n">
-        <v>7.61</v>
+        <v>5.87</v>
       </c>
       <c r="K20" t="n">
-        <v>120.3</v>
+        <v>118.2</v>
       </c>
       <c r="L20" t="n">
-        <v>4.97</v>
+        <v>0.41</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>465.5</v>
+        <v>52.2</v>
       </c>
       <c r="O20" t="n">
-        <v>651.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>837.9</v>
+        <v>94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1024.1</v>
+        <v>114.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1210.3</v>
+        <v>135.7</v>
       </c>
       <c r="S20" t="n">
-        <v>1396.5</v>
+        <v>156.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>超豐</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>561</v>
+        <v>140</v>
       </c>
       <c r="D21" t="n">
-        <v>5.22</v>
+        <v>4.67</v>
       </c>
       <c r="E21" t="n">
-        <v>107.47</v>
+        <v>29.98</v>
       </c>
       <c r="F21" t="n">
-        <v>9.59</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>50.1</v>
+        <v>45.7</v>
       </c>
       <c r="I21" t="n">
-        <v>1020.5</v>
+        <v>206.4</v>
       </c>
       <c r="J21" t="n">
-        <v>5.87</v>
+        <v>5.31</v>
       </c>
       <c r="K21" t="n">
-        <v>107.47</v>
+        <v>30.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.08</v>
+        <v>2.14</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>52.2</v>
+        <v>46.7</v>
       </c>
       <c r="O21" t="n">
-        <v>73.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>94</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>114.8</v>
+        <v>102.7</v>
       </c>
       <c r="R21" t="n">
-        <v>135.7</v>
+        <v>121.4</v>
       </c>
       <c r="S21" t="n">
-        <v>156.6</v>
+        <v>140.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/PE買入區間監看.xlsx
+++ b/data/PE買入區間監看.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,43 +529,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.7</v>
+        <v>136</v>
       </c>
       <c r="D2" t="n">
-        <v>3.84</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>13.2</v>
+        <v>14.53</v>
       </c>
       <c r="F2" t="n">
-        <v>18.26</v>
+        <v>23.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>70.09999999999999</v>
+        <v>221.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-27.7</v>
+        <v>-38.7</v>
       </c>
       <c r="J2" t="n">
-        <v>12.83</v>
+        <v>14.53</v>
       </c>
       <c r="K2" t="n">
-        <v>45.6</v>
+        <v>1126.92</v>
       </c>
       <c r="L2" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -573,64 +573,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>38.4</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>53.8</v>
+        <v>131</v>
       </c>
       <c r="P2" t="n">
-        <v>69.09999999999999</v>
+        <v>168.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>84.5</v>
+        <v>205.9</v>
       </c>
       <c r="R2" t="n">
-        <v>99.8</v>
+        <v>243.4</v>
       </c>
       <c r="S2" t="n">
-        <v>115.2</v>
+        <v>280.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>豆府</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>178.5</v>
+        <v>288</v>
       </c>
       <c r="D3" t="n">
-        <v>15.28</v>
+        <v>18.46</v>
       </c>
       <c r="E3" t="n">
-        <v>11.68</v>
+        <v>15.6</v>
       </c>
       <c r="F3" t="n">
-        <v>13.79</v>
+        <v>16.77</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>210.7</v>
+        <v>309.6</v>
       </c>
       <c r="I3" t="n">
-        <v>-15.3</v>
+        <v>-7</v>
       </c>
       <c r="J3" t="n">
-        <v>11.19</v>
+        <v>15.47</v>
       </c>
       <c r="K3" t="n">
-        <v>29.38</v>
+        <v>21.48</v>
       </c>
       <c r="L3" t="n">
-        <v>7.56</v>
+        <v>5.48</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -638,64 +638,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>152.8</v>
+        <v>184.6</v>
       </c>
       <c r="O3" t="n">
-        <v>213.9</v>
+        <v>258.4</v>
       </c>
       <c r="P3" t="n">
-        <v>275</v>
+        <v>332.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>336.2</v>
+        <v>406.1</v>
       </c>
       <c r="R3" t="n">
-        <v>397.3</v>
+        <v>480</v>
       </c>
       <c r="S3" t="n">
-        <v>458.4</v>
+        <v>553.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>豆府</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.3</v>
+        <v>178.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.91</v>
+        <v>15.28</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>11.68</v>
       </c>
       <c r="F4" t="n">
-        <v>26.68</v>
+        <v>13.79</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>104.3</v>
+        <v>210.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-28.8</v>
+        <v>-15.3</v>
       </c>
       <c r="J4" t="n">
-        <v>16.62</v>
+        <v>11.19</v>
       </c>
       <c r="K4" t="n">
-        <v>61.2</v>
+        <v>29.38</v>
       </c>
       <c r="L4" t="n">
-        <v>5.06</v>
+        <v>7.56</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -703,64 +703,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>39.1</v>
+        <v>152.8</v>
       </c>
       <c r="O4" t="n">
-        <v>54.7</v>
+        <v>213.9</v>
       </c>
       <c r="P4" t="n">
-        <v>70.40000000000001</v>
+        <v>275</v>
       </c>
       <c r="Q4" t="n">
-        <v>86</v>
+        <v>336.2</v>
       </c>
       <c r="R4" t="n">
-        <v>101.7</v>
+        <v>397.3</v>
       </c>
       <c r="S4" t="n">
-        <v>117.3</v>
+        <v>458.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.40000000000001</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
-        <v>4.41</v>
+        <v>10.96</v>
       </c>
       <c r="E5" t="n">
-        <v>14.6</v>
+        <v>20.16</v>
       </c>
       <c r="F5" t="n">
-        <v>19.08</v>
+        <v>23.51</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>84.09999999999999</v>
+        <v>257.6</v>
       </c>
       <c r="I5" t="n">
-        <v>-23.5</v>
+        <v>-14.2</v>
       </c>
       <c r="J5" t="n">
-        <v>13.49</v>
+        <v>18.84</v>
       </c>
       <c r="K5" t="n">
-        <v>85.66</v>
+        <v>37.25</v>
       </c>
       <c r="L5" t="n">
-        <v>3.19</v>
+        <v>4.03</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -768,64 +768,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>44.1</v>
+        <v>109.6</v>
       </c>
       <c r="O5" t="n">
-        <v>61.7</v>
+        <v>153.4</v>
       </c>
       <c r="P5" t="n">
-        <v>79.40000000000001</v>
+        <v>197.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>97</v>
+        <v>241.1</v>
       </c>
       <c r="R5" t="n">
-        <v>114.7</v>
+        <v>285</v>
       </c>
       <c r="S5" t="n">
-        <v>132.3</v>
+        <v>328.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.5</v>
+        <v>116</v>
       </c>
       <c r="D6" t="n">
-        <v>6.39</v>
+        <v>8.24</v>
       </c>
       <c r="E6" t="n">
-        <v>12.91</v>
+        <v>14.08</v>
       </c>
       <c r="F6" t="n">
-        <v>13.44</v>
+        <v>17.58</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>85.90000000000001</v>
+        <v>144.8</v>
       </c>
       <c r="I6" t="n">
-        <v>-4</v>
+        <v>-19.9</v>
       </c>
       <c r="J6" t="n">
-        <v>12.04</v>
+        <v>12.24</v>
       </c>
       <c r="K6" t="n">
-        <v>19.29</v>
+        <v>453.08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.06</v>
+        <v>3.77</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -833,64 +833,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>63.9</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>89.5</v>
+        <v>115.4</v>
       </c>
       <c r="P6" t="n">
-        <v>115</v>
+        <v>148.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>140.6</v>
+        <v>181.3</v>
       </c>
       <c r="R6" t="n">
-        <v>166.1</v>
+        <v>214.2</v>
       </c>
       <c r="S6" t="n">
-        <v>191.7</v>
+        <v>247.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1450</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>81.16</v>
+        <v>4.41</v>
       </c>
       <c r="E7" t="n">
-        <v>17.87</v>
+        <v>14.6</v>
       </c>
       <c r="F7" t="n">
-        <v>20.74</v>
+        <v>19.08</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1682.9</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.8</v>
+        <v>-23.5</v>
       </c>
       <c r="J7" t="n">
-        <v>11.54</v>
+        <v>13.49</v>
       </c>
       <c r="K7" t="n">
-        <v>89.78</v>
+        <v>85.66</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -898,87 +898,607 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>811.6</v>
+        <v>44.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1136.2</v>
+        <v>61.7</v>
       </c>
       <c r="P7" t="n">
-        <v>1460.9</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>1785.5</v>
+        <v>97</v>
       </c>
       <c r="R7" t="n">
-        <v>2110.2</v>
+        <v>114.7</v>
       </c>
       <c r="S7" t="n">
-        <v>2434.8</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>大樹</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="K8" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>86</v>
+      </c>
+      <c r="R8" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>117.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>9911</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>櫻花</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>191.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>訊連</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>69</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="E10" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-27.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="K10" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>81</v>
+      </c>
+      <c r="R10" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>110.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D11" t="n">
+        <v>81.16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="F11" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1682.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="K11" t="n">
+        <v>89.78</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>811.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1136.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1460.9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1785.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2110.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2434.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3687</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>歐買尬</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>78</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="K12" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>62</v>
+      </c>
+      <c r="P12" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>132.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>一零四</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" t="n">
+        <v>231.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="K13" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>150.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>271.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>331.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>392.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>452.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="K14" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>6690</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>安碁資訊</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C15" t="n">
         <v>179.5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D15" t="n">
         <v>10.62</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E15" t="n">
         <v>16.9</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F15" t="n">
         <v>17.31</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G15" t="n">
         <v>15</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H15" t="n">
         <v>183.8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I15" t="n">
         <v>-2.3</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J15" t="n">
         <v>14.26</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K15" t="n">
         <v>31.4</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L15" t="n">
         <v>5.01</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
         <v>106.2</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O15" t="n">
         <v>148.7</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P15" t="n">
         <v>191.2</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q15" t="n">
         <v>233.6</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R15" t="n">
         <v>276.1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S15" t="n">
         <v>318.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="E16" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="F16" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19</v>
+      </c>
+      <c r="H16" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="K16" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="P16" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>142.8</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +1512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1095,43 +1615,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.7</v>
+        <v>136</v>
       </c>
       <c r="D2" t="n">
-        <v>3.84</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>13.2</v>
+        <v>14.53</v>
       </c>
       <c r="F2" t="n">
-        <v>18.26</v>
+        <v>23.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>70.09999999999999</v>
+        <v>221.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-27.7</v>
+        <v>-38.7</v>
       </c>
       <c r="J2" t="n">
-        <v>12.83</v>
+        <v>14.53</v>
       </c>
       <c r="K2" t="n">
-        <v>45.6</v>
+        <v>1126.92</v>
       </c>
       <c r="L2" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1139,64 +1659,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>38.4</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>53.8</v>
+        <v>131</v>
       </c>
       <c r="P2" t="n">
-        <v>69.09999999999999</v>
+        <v>168.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>84.5</v>
+        <v>205.9</v>
       </c>
       <c r="R2" t="n">
-        <v>99.8</v>
+        <v>243.4</v>
       </c>
       <c r="S2" t="n">
-        <v>115.2</v>
+        <v>280.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>豆府</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>178.5</v>
+        <v>288</v>
       </c>
       <c r="D3" t="n">
-        <v>15.28</v>
+        <v>18.46</v>
       </c>
       <c r="E3" t="n">
-        <v>11.68</v>
+        <v>15.6</v>
       </c>
       <c r="F3" t="n">
-        <v>13.79</v>
+        <v>16.77</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>210.7</v>
+        <v>309.6</v>
       </c>
       <c r="I3" t="n">
-        <v>-15.3</v>
+        <v>-7</v>
       </c>
       <c r="J3" t="n">
-        <v>11.19</v>
+        <v>15.47</v>
       </c>
       <c r="K3" t="n">
-        <v>29.38</v>
+        <v>21.48</v>
       </c>
       <c r="L3" t="n">
-        <v>7.56</v>
+        <v>5.48</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1204,64 +1724,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>152.8</v>
+        <v>184.6</v>
       </c>
       <c r="O3" t="n">
-        <v>213.9</v>
+        <v>258.4</v>
       </c>
       <c r="P3" t="n">
-        <v>275</v>
+        <v>332.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>336.2</v>
+        <v>406.1</v>
       </c>
       <c r="R3" t="n">
-        <v>397.3</v>
+        <v>480</v>
       </c>
       <c r="S3" t="n">
-        <v>458.4</v>
+        <v>553.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>豆府</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.3</v>
+        <v>178.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.91</v>
+        <v>15.28</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>11.68</v>
       </c>
       <c r="F4" t="n">
-        <v>26.68</v>
+        <v>13.79</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>104.3</v>
+        <v>210.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-28.8</v>
+        <v>-15.3</v>
       </c>
       <c r="J4" t="n">
-        <v>16.62</v>
+        <v>11.19</v>
       </c>
       <c r="K4" t="n">
-        <v>61.2</v>
+        <v>29.38</v>
       </c>
       <c r="L4" t="n">
-        <v>5.06</v>
+        <v>7.56</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1269,64 +1789,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>39.1</v>
+        <v>152.8</v>
       </c>
       <c r="O4" t="n">
-        <v>54.7</v>
+        <v>213.9</v>
       </c>
       <c r="P4" t="n">
-        <v>70.40000000000001</v>
+        <v>275</v>
       </c>
       <c r="Q4" t="n">
-        <v>86</v>
+        <v>336.2</v>
       </c>
       <c r="R4" t="n">
-        <v>101.7</v>
+        <v>397.3</v>
       </c>
       <c r="S4" t="n">
-        <v>117.3</v>
+        <v>458.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.40000000000001</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
-        <v>4.41</v>
+        <v>10.96</v>
       </c>
       <c r="E5" t="n">
-        <v>14.6</v>
+        <v>20.16</v>
       </c>
       <c r="F5" t="n">
-        <v>19.08</v>
+        <v>23.51</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>84.09999999999999</v>
+        <v>257.6</v>
       </c>
       <c r="I5" t="n">
-        <v>-23.5</v>
+        <v>-14.2</v>
       </c>
       <c r="J5" t="n">
-        <v>13.49</v>
+        <v>18.84</v>
       </c>
       <c r="K5" t="n">
-        <v>85.66</v>
+        <v>37.25</v>
       </c>
       <c r="L5" t="n">
-        <v>3.19</v>
+        <v>4.03</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1334,64 +1854,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>44.1</v>
+        <v>109.6</v>
       </c>
       <c r="O5" t="n">
-        <v>61.7</v>
+        <v>153.4</v>
       </c>
       <c r="P5" t="n">
-        <v>79.40000000000001</v>
+        <v>197.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>97</v>
+        <v>241.1</v>
       </c>
       <c r="R5" t="n">
-        <v>114.7</v>
+        <v>285</v>
       </c>
       <c r="S5" t="n">
-        <v>132.3</v>
+        <v>328.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.5</v>
+        <v>116</v>
       </c>
       <c r="D6" t="n">
-        <v>6.39</v>
+        <v>8.24</v>
       </c>
       <c r="E6" t="n">
-        <v>12.91</v>
+        <v>14.08</v>
       </c>
       <c r="F6" t="n">
-        <v>13.44</v>
+        <v>17.58</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>85.90000000000001</v>
+        <v>144.8</v>
       </c>
       <c r="I6" t="n">
-        <v>-4</v>
+        <v>-19.9</v>
       </c>
       <c r="J6" t="n">
-        <v>12.04</v>
+        <v>12.24</v>
       </c>
       <c r="K6" t="n">
-        <v>19.29</v>
+        <v>453.08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.06</v>
+        <v>3.77</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1399,64 +1919,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>63.9</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>89.5</v>
+        <v>115.4</v>
       </c>
       <c r="P6" t="n">
-        <v>115</v>
+        <v>148.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>140.6</v>
+        <v>181.3</v>
       </c>
       <c r="R6" t="n">
-        <v>166.1</v>
+        <v>214.2</v>
       </c>
       <c r="S6" t="n">
-        <v>191.7</v>
+        <v>247.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1450</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>81.16</v>
+        <v>4.41</v>
       </c>
       <c r="E7" t="n">
-        <v>17.87</v>
+        <v>14.6</v>
       </c>
       <c r="F7" t="n">
-        <v>20.74</v>
+        <v>19.08</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1682.9</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.8</v>
+        <v>-23.5</v>
       </c>
       <c r="J7" t="n">
-        <v>11.54</v>
+        <v>13.49</v>
       </c>
       <c r="K7" t="n">
-        <v>89.78</v>
+        <v>85.66</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1464,64 +1984,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>811.6</v>
+        <v>44.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1136.2</v>
+        <v>61.7</v>
       </c>
       <c r="P7" t="n">
-        <v>1460.9</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>1785.5</v>
+        <v>97</v>
       </c>
       <c r="R7" t="n">
-        <v>2110.2</v>
+        <v>114.7</v>
       </c>
       <c r="S7" t="n">
-        <v>2434.8</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>179.5</v>
+        <v>74.3</v>
       </c>
       <c r="D8" t="n">
-        <v>10.62</v>
+        <v>3.91</v>
       </c>
       <c r="E8" t="n">
-        <v>16.9</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>17.31</v>
+        <v>26.68</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>183.8</v>
+        <v>104.3</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3</v>
+        <v>-28.8</v>
       </c>
       <c r="J8" t="n">
-        <v>14.26</v>
+        <v>16.62</v>
       </c>
       <c r="K8" t="n">
-        <v>31.4</v>
+        <v>61.2</v>
       </c>
       <c r="L8" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1529,64 +2049,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>106.2</v>
+        <v>39.1</v>
       </c>
       <c r="O8" t="n">
-        <v>148.7</v>
+        <v>54.7</v>
       </c>
       <c r="P8" t="n">
-        <v>191.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>233.6</v>
+        <v>86</v>
       </c>
       <c r="R8" t="n">
-        <v>276.1</v>
+        <v>101.7</v>
       </c>
       <c r="S8" t="n">
-        <v>318.6</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>636</v>
+        <v>82.5</v>
       </c>
       <c r="D9" t="n">
-        <v>31.45</v>
+        <v>6.39</v>
       </c>
       <c r="E9" t="n">
-        <v>20.22</v>
+        <v>12.91</v>
       </c>
       <c r="F9" t="n">
-        <v>18.15</v>
+        <v>13.44</v>
       </c>
       <c r="G9" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>570.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>11.4</v>
+        <v>-4</v>
       </c>
       <c r="J9" t="n">
-        <v>14.17</v>
+        <v>12.04</v>
       </c>
       <c r="K9" t="n">
-        <v>31.63</v>
+        <v>19.29</v>
       </c>
       <c r="L9" t="n">
-        <v>4.01</v>
+        <v>6.06</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1594,64 +2114,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>314.5</v>
+        <v>63.9</v>
       </c>
       <c r="O9" t="n">
-        <v>440.3</v>
+        <v>89.5</v>
       </c>
       <c r="P9" t="n">
-        <v>566.1</v>
+        <v>115</v>
       </c>
       <c r="Q9" t="n">
-        <v>691.9</v>
+        <v>140.6</v>
       </c>
       <c r="R9" t="n">
-        <v>817.7</v>
+        <v>166.1</v>
       </c>
       <c r="S9" t="n">
-        <v>943.5</v>
+        <v>191.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>112.5</v>
+        <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>7.94</v>
+        <v>3.68</v>
       </c>
       <c r="E10" t="n">
-        <v>14.17</v>
+        <v>18.75</v>
       </c>
       <c r="F10" t="n">
-        <v>8.289999999999999</v>
+        <v>25.86</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>65.8</v>
+        <v>95.2</v>
       </c>
       <c r="I10" t="n">
-        <v>70.90000000000001</v>
+        <v>-27.5</v>
       </c>
       <c r="J10" t="n">
-        <v>6.23</v>
+        <v>16.49</v>
       </c>
       <c r="K10" t="n">
-        <v>29.13</v>
+        <v>56.5</v>
       </c>
       <c r="L10" t="n">
-        <v>3.38</v>
+        <v>5.22</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1659,64 +2179,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>79.40000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="O10" t="n">
-        <v>111.2</v>
+        <v>51.5</v>
       </c>
       <c r="P10" t="n">
-        <v>142.9</v>
+        <v>66.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>174.7</v>
+        <v>81</v>
       </c>
       <c r="R10" t="n">
-        <v>206.4</v>
+        <v>95.7</v>
       </c>
       <c r="S10" t="n">
-        <v>238.2</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>778</v>
+        <v>1450</v>
       </c>
       <c r="D11" t="n">
-        <v>40.37</v>
+        <v>81.16</v>
       </c>
       <c r="E11" t="n">
-        <v>19.27</v>
+        <v>17.87</v>
       </c>
       <c r="F11" t="n">
-        <v>11.13</v>
+        <v>20.74</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>449.4</v>
+        <v>1682.9</v>
       </c>
       <c r="I11" t="n">
-        <v>73.09999999999999</v>
+        <v>-13.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.92</v>
+        <v>11.54</v>
       </c>
       <c r="K11" t="n">
-        <v>30.21</v>
+        <v>89.78</v>
       </c>
       <c r="L11" t="n">
-        <v>4.63</v>
+        <v>3.09</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1724,64 +2244,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>403.7</v>
+        <v>811.6</v>
       </c>
       <c r="O11" t="n">
-        <v>565.2</v>
+        <v>1136.2</v>
       </c>
       <c r="P11" t="n">
-        <v>726.7</v>
+        <v>1460.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>888.1</v>
+        <v>1785.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1049.6</v>
+        <v>2110.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1211.1</v>
+        <v>2434.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>歐買尬</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>788</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>55.96</v>
+        <v>4.43</v>
       </c>
       <c r="E12" t="n">
-        <v>14.08</v>
+        <v>17.61</v>
       </c>
       <c r="F12" t="n">
-        <v>6.45</v>
+        <v>30.96</v>
       </c>
       <c r="G12" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>360.8</v>
+        <v>137.1</v>
       </c>
       <c r="I12" t="n">
-        <v>118.4</v>
+        <v>-43.1</v>
       </c>
       <c r="J12" t="n">
-        <v>4.31</v>
+        <v>13.26</v>
       </c>
       <c r="K12" t="n">
-        <v>111.49</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>5.33</v>
+        <v>2.57</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1789,64 +2309,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>559.6</v>
+        <v>44.3</v>
       </c>
       <c r="O12" t="n">
-        <v>783.4</v>
+        <v>62</v>
       </c>
       <c r="P12" t="n">
-        <v>1007.3</v>
+        <v>79.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1231.1</v>
+        <v>97.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1455</v>
+        <v>115.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1678.8</v>
+        <v>132.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>一零四</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>154.5</v>
+        <v>223.5</v>
       </c>
       <c r="D13" t="n">
-        <v>8.390000000000001</v>
+        <v>15.08</v>
       </c>
       <c r="E13" t="n">
-        <v>18.41</v>
+        <v>14.82</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>15.38</v>
       </c>
       <c r="G13" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>117.5</v>
+        <v>231.9</v>
       </c>
       <c r="I13" t="n">
-        <v>31.5</v>
+        <v>-3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>10.9</v>
+        <v>13.43</v>
       </c>
       <c r="K13" t="n">
-        <v>23.27</v>
+        <v>21.94</v>
       </c>
       <c r="L13" t="n">
-        <v>5.05</v>
+        <v>6.56</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1854,64 +2374,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>83.90000000000001</v>
+        <v>150.8</v>
       </c>
       <c r="O13" t="n">
-        <v>117.5</v>
+        <v>211.1</v>
       </c>
       <c r="P13" t="n">
-        <v>151</v>
+        <v>271.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>184.6</v>
+        <v>331.8</v>
       </c>
       <c r="R13" t="n">
-        <v>218.1</v>
+        <v>392.1</v>
       </c>
       <c r="S13" t="n">
-        <v>251.7</v>
+        <v>452.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2420</v>
+        <v>35.8</v>
       </c>
       <c r="D14" t="n">
-        <v>61.06</v>
+        <v>2.12</v>
       </c>
       <c r="E14" t="n">
-        <v>39.63</v>
+        <v>16.89</v>
       </c>
       <c r="F14" t="n">
-        <v>11.68</v>
+        <v>17.29</v>
       </c>
       <c r="G14" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>713.4</v>
+        <v>36.7</v>
       </c>
       <c r="I14" t="n">
-        <v>239.2</v>
+        <v>-2.3</v>
       </c>
       <c r="J14" t="n">
-        <v>8.91</v>
+        <v>14.48</v>
       </c>
       <c r="K14" t="n">
-        <v>59.89</v>
+        <v>23.18</v>
       </c>
       <c r="L14" t="n">
-        <v>0.87</v>
+        <v>3.95</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1919,64 +2439,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>610.6</v>
+        <v>21.2</v>
       </c>
       <c r="O14" t="n">
-        <v>854.8</v>
+        <v>29.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1099.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1343.3</v>
+        <v>46.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1587.6</v>
+        <v>55.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1831.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2150</v>
+        <v>179.5</v>
       </c>
       <c r="D15" t="n">
-        <v>27.11</v>
+        <v>10.62</v>
       </c>
       <c r="E15" t="n">
-        <v>79.31</v>
+        <v>16.9</v>
       </c>
       <c r="F15" t="n">
-        <v>24.02</v>
+        <v>17.31</v>
       </c>
       <c r="G15" t="n">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="H15" t="n">
-        <v>651.1</v>
+        <v>183.8</v>
       </c>
       <c r="I15" t="n">
-        <v>230.2</v>
+        <v>-2.3</v>
       </c>
       <c r="J15" t="n">
-        <v>20.41</v>
+        <v>14.26</v>
       </c>
       <c r="K15" t="n">
-        <v>98.53</v>
+        <v>31.4</v>
       </c>
       <c r="L15" t="n">
-        <v>0.54</v>
+        <v>5.01</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1984,64 +2504,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>271.1</v>
+        <v>106.2</v>
       </c>
       <c r="O15" t="n">
-        <v>379.5</v>
+        <v>148.7</v>
       </c>
       <c r="P15" t="n">
-        <v>488</v>
+        <v>191.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>596.4</v>
+        <v>233.6</v>
       </c>
       <c r="R15" t="n">
-        <v>704.9</v>
+        <v>276.1</v>
       </c>
       <c r="S15" t="n">
-        <v>813.3</v>
+        <v>318.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2595</v>
+        <v>90.3</v>
       </c>
       <c r="D16" t="n">
-        <v>52.88</v>
+        <v>4.76</v>
       </c>
       <c r="E16" t="n">
-        <v>49.07</v>
+        <v>18.97</v>
       </c>
       <c r="F16" t="n">
-        <v>25.4</v>
+        <v>19.05</v>
       </c>
       <c r="G16" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="H16" t="n">
-        <v>1343.4</v>
+        <v>90.7</v>
       </c>
       <c r="I16" t="n">
-        <v>93.2</v>
+        <v>-0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>17.64</v>
+        <v>15.27</v>
       </c>
       <c r="K16" t="n">
-        <v>56.76</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.58</v>
+        <v>4.98</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2049,64 +2569,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>528.8</v>
+        <v>47.6</v>
       </c>
       <c r="O16" t="n">
-        <v>740.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>951.8</v>
+        <v>85.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1163.4</v>
+        <v>104.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1374.9</v>
+        <v>123.8</v>
       </c>
       <c r="S16" t="n">
-        <v>1586.4</v>
+        <v>142.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長聖</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2510</v>
+        <v>142.5</v>
       </c>
       <c r="D17" t="n">
-        <v>74.39</v>
+        <v>5.27</v>
       </c>
       <c r="E17" t="n">
-        <v>33.74</v>
+        <v>27.04</v>
       </c>
       <c r="F17" t="n">
-        <v>15.69</v>
+        <v>26.98</v>
       </c>
       <c r="G17" t="n">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
-        <v>1167.3</v>
+        <v>142.2</v>
       </c>
       <c r="I17" t="n">
-        <v>115</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
-        <v>12.54</v>
+        <v>22.35</v>
       </c>
       <c r="K17" t="n">
-        <v>35.51</v>
+        <v>1814.71</v>
       </c>
       <c r="L17" t="n">
-        <v>0.88</v>
+        <v>2.81</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2114,64 +2634,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>743.9</v>
+        <v>52.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1041.5</v>
+        <v>73.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1339</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>1636.6</v>
+        <v>115.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1934.1</v>
+        <v>137</v>
       </c>
       <c r="S17" t="n">
-        <v>2231.7</v>
+        <v>158.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5825</v>
+        <v>190</v>
       </c>
       <c r="D18" t="n">
-        <v>46.55</v>
+        <v>13.48</v>
       </c>
       <c r="E18" t="n">
-        <v>125.13</v>
+        <v>14.09</v>
       </c>
       <c r="F18" t="n">
-        <v>13.3</v>
+        <v>13.02</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="H18" t="n">
-        <v>619.1</v>
+        <v>175.5</v>
       </c>
       <c r="I18" t="n">
-        <v>840.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>7.61</v>
+        <v>6.14</v>
       </c>
       <c r="K18" t="n">
-        <v>125.13</v>
+        <v>26.18</v>
       </c>
       <c r="L18" t="n">
-        <v>0.43</v>
+        <v>6.42</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2179,64 +2699,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>465.5</v>
+        <v>134.8</v>
       </c>
       <c r="O18" t="n">
-        <v>651.7</v>
+        <v>188.7</v>
       </c>
       <c r="P18" t="n">
-        <v>837.9</v>
+        <v>242.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>1024.1</v>
+        <v>296.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1210.3</v>
+        <v>350.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1396.5</v>
+        <v>404.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>353</v>
+        <v>122</v>
       </c>
       <c r="D19" t="n">
-        <v>10.25</v>
+        <v>9.41</v>
       </c>
       <c r="E19" t="n">
-        <v>34.44</v>
+        <v>12.96</v>
       </c>
       <c r="F19" t="n">
-        <v>14.07</v>
+        <v>12.63</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="H19" t="n">
-        <v>144.3</v>
+        <v>118.8</v>
       </c>
       <c r="I19" t="n">
-        <v>144.7</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
-        <v>9.109999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="K19" t="n">
-        <v>34.44</v>
+        <v>26.73</v>
       </c>
       <c r="L19" t="n">
-        <v>1.98</v>
+        <v>4.51</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2244,64 +2764,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>102.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>143.5</v>
+        <v>131.7</v>
       </c>
       <c r="P19" t="n">
-        <v>184.5</v>
+        <v>169.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>225.5</v>
+        <v>207</v>
       </c>
       <c r="R19" t="n">
-        <v>266.5</v>
+        <v>244.7</v>
       </c>
       <c r="S19" t="n">
-        <v>307.5</v>
+        <v>282.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>叡揚</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>617</v>
+        <v>100.5</v>
       </c>
       <c r="D20" t="n">
-        <v>5.22</v>
+        <v>7.58</v>
       </c>
       <c r="E20" t="n">
-        <v>118.2</v>
+        <v>13.26</v>
       </c>
       <c r="F20" t="n">
-        <v>9.59</v>
+        <v>11.96</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="H20" t="n">
-        <v>50.1</v>
+        <v>90.7</v>
       </c>
       <c r="I20" t="n">
-        <v>1132.3</v>
+        <v>10.9</v>
       </c>
       <c r="J20" t="n">
-        <v>5.87</v>
+        <v>8.73</v>
       </c>
       <c r="K20" t="n">
-        <v>118.2</v>
+        <v>32.4</v>
       </c>
       <c r="L20" t="n">
-        <v>0.41</v>
+        <v>4.78</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2309,87 +2829,5417 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>52.2</v>
+        <v>75.8</v>
       </c>
       <c r="O20" t="n">
-        <v>73.09999999999999</v>
+        <v>106.1</v>
       </c>
       <c r="P20" t="n">
-        <v>94</v>
+        <v>136.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>114.8</v>
+        <v>166.8</v>
       </c>
       <c r="R20" t="n">
-        <v>135.7</v>
+        <v>197.1</v>
       </c>
       <c r="S20" t="n">
-        <v>156.6</v>
+        <v>227.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>140</v>
+        <v>116.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4.67</v>
+        <v>6.78</v>
       </c>
       <c r="E21" t="n">
-        <v>29.98</v>
+        <v>17.18</v>
       </c>
       <c r="F21" t="n">
-        <v>9.779999999999999</v>
+        <v>16.94</v>
       </c>
       <c r="G21" t="n">
+        <v>31</v>
+      </c>
+      <c r="H21" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="K21" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>176.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>203.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5607</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>遠雄港</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="F22" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="G22" t="n">
+        <v>32</v>
+      </c>
+      <c r="H22" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="K22" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6721</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>信實</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="G23" t="n">
+        <v>32</v>
+      </c>
+      <c r="H23" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="K23" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="S23" t="n">
+        <v>142.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>寶雅</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>636</v>
+      </c>
+      <c r="D24" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="F24" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="G24" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" t="n">
+        <v>570.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K24" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>440.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>566.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>691.9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>817.7</v>
+      </c>
+      <c r="S24" t="n">
+        <v>943.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4114</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>健喬</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E25" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="F25" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>41</v>
+      </c>
+      <c r="H25" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="K25" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="S25" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4772</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>台特化</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>283</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="E26" t="n">
+        <v>58.47</v>
+      </c>
+      <c r="F26" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="G26" t="n">
+        <v>41</v>
+      </c>
+      <c r="H26" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="K26" t="n">
+        <v>110.97</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="S26" t="n">
+        <v>145.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6791</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>虎門科技</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>105</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="E27" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H27" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="K27" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="S27" t="n">
+        <v>146.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2363</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>矽統</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="G28" t="n">
+        <v>50</v>
+      </c>
+      <c r="H28" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="K28" t="n">
+        <v>179</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>17</v>
+      </c>
+      <c r="O28" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>52</v>
+      </c>
+      <c r="H29" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K29" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>214</v>
+      </c>
+      <c r="O29" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="P29" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>470.8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>556.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="E30" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="G30" t="n">
+        <v>52</v>
+      </c>
+      <c r="H30" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="K30" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="O30" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>203.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="E31" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="G31" t="n">
+        <v>55</v>
+      </c>
+      <c r="H31" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>48</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="K31" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>44</v>
+      </c>
+      <c r="P31" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="R31" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="S31" t="n">
+        <v>94.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4953</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>緯軟</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="E32" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="G32" t="n">
+        <v>56</v>
+      </c>
+      <c r="H32" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="K32" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="O32" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>240.8</v>
+      </c>
+      <c r="S32" t="n">
+        <v>277.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2889</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>國票金</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E33" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="F33" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="G33" t="n">
+        <v>56</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="K33" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P33" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="R33" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="G34" t="n">
+        <v>58</v>
+      </c>
+      <c r="H34" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>202.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>239.7</v>
+      </c>
+      <c r="S34" t="n">
+        <v>276.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E35" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="G35" t="n">
+        <v>59</v>
+      </c>
+      <c r="H35" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="K35" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="R35" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="S35" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="E36" t="n">
+        <v>67.34</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="G36" t="n">
+        <v>59</v>
+      </c>
+      <c r="H36" t="n">
+        <v>686.4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="K36" t="n">
+        <v>510.49</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>227.6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>357.7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>422.8</v>
+      </c>
+      <c r="S36" t="n">
+        <v>487.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5903</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>189</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="E37" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="F37" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="G37" t="n">
+        <v>60</v>
+      </c>
+      <c r="H37" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>32</v>
+      </c>
+      <c r="J37" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="O37" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="P37" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>181</v>
+      </c>
+      <c r="S37" t="n">
+        <v>208.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3162</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>精確</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E38" t="n">
+        <v>69.34</v>
+      </c>
+      <c r="F38" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="G38" t="n">
+        <v>61</v>
+      </c>
+      <c r="H38" t="n">
+        <v>32</v>
+      </c>
+      <c r="I38" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="K38" t="n">
+        <v>397.14</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="S38" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>群益證</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E39" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="G39" t="n">
+        <v>62</v>
+      </c>
+      <c r="H39" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K39" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="O39" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="R39" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="S39" t="n">
+        <v>107.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="E40" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>63</v>
+      </c>
+      <c r="H40" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="K40" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="O40" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="P40" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>238.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>中興電</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>181</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="E41" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="F41" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="G41" t="n">
+        <v>64</v>
+      </c>
+      <c r="H41" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="K41" t="n">
+        <v>64.83</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="O41" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>148.1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>214</v>
+      </c>
+      <c r="S41" t="n">
+        <v>246.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>778</v>
+      </c>
+      <c r="D42" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="E42" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="G42" t="n">
+        <v>65</v>
+      </c>
+      <c r="H42" t="n">
+        <v>449.4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="K42" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="L42" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>403.7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>565.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>726.7</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>888.1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1049.6</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1211.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1075</v>
+      </c>
+      <c r="D43" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="E43" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="F43" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="G43" t="n">
+        <v>66</v>
+      </c>
+      <c r="H43" t="n">
+        <v>461.8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="K43" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>632.7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>773.3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>913.9</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1054.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4116</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>明基醫</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E44" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="F44" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="G44" t="n">
+        <v>66</v>
+      </c>
+      <c r="H44" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J44" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="K44" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="L44" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="O44" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="R44" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="S44" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2947</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>振宇五金</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E45" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F45" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="G45" t="n">
+        <v>67</v>
+      </c>
+      <c r="H45" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="K45" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="P45" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>89.09999999999999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2755</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>揚秦</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="G46" t="n">
+        <v>68</v>
+      </c>
+      <c r="H46" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="K46" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>70</v>
+      </c>
+      <c r="O46" t="n">
+        <v>98</v>
+      </c>
+      <c r="P46" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>154</v>
+      </c>
+      <c r="R46" t="n">
+        <v>182</v>
+      </c>
+      <c r="S46" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>225</v>
+      </c>
+      <c r="D47" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="G47" t="n">
+        <v>69</v>
+      </c>
+      <c r="H47" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="I47" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="K47" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>145</v>
+      </c>
+      <c r="O47" t="n">
+        <v>203</v>
+      </c>
+      <c r="P47" t="n">
+        <v>261</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>319</v>
+      </c>
+      <c r="R47" t="n">
+        <v>377</v>
+      </c>
+      <c r="S47" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>亞光</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>163</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="E48" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="F48" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="G48" t="n">
+        <v>69</v>
+      </c>
+      <c r="H48" t="n">
+        <v>126</v>
+      </c>
+      <c r="I48" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="K48" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="O48" t="n">
+        <v>96</v>
+      </c>
+      <c r="P48" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="R48" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>205.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>788</v>
+      </c>
+      <c r="D49" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="E49" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="G49" t="n">
+        <v>71</v>
+      </c>
+      <c r="H49" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="I49" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K49" t="n">
+        <v>111.49</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>559.6</v>
+      </c>
+      <c r="O49" t="n">
+        <v>783.4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1007.3</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1231.1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1455</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1678.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>8284</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>三竹</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="E50" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F50" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="G50" t="n">
+        <v>77</v>
+      </c>
+      <c r="H50" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J50" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="K50" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>64</v>
+      </c>
+      <c r="P50" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="R50" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="S50" t="n">
+        <v>137.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>邁達特</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E51" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="F51" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="G51" t="n">
+        <v>77</v>
+      </c>
+      <c r="H51" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5670</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O51" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="P51" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="S51" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4977</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>眾達-KY</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>191</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="E52" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="F52" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="G52" t="n">
+        <v>78</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="I52" t="n">
+        <v>276.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="K52" t="n">
+        <v>450</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="P52" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="S52" t="n">
+        <v>138.3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>宏碁</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>34</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E53" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="G53" t="n">
+        <v>79</v>
+      </c>
+      <c r="H53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="K53" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O53" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P53" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>29</v>
+      </c>
+      <c r="R53" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="S53" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2480</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>敦陽科</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E54" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F54" t="n">
+        <v>14</v>
+      </c>
+      <c r="G54" t="n">
+        <v>80</v>
+      </c>
+      <c r="H54" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K54" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="L54" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="O54" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="P54" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="R54" t="n">
+        <v>218.1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>251.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>長榮航太</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="E55" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="F55" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="G55" t="n">
+        <v>80</v>
+      </c>
+      <c r="H55" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J55" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="P55" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="S55" t="n">
+        <v>196.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D56" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="E56" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="F56" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="G56" t="n">
+        <v>82</v>
+      </c>
+      <c r="H56" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="I56" t="n">
+        <v>226.2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="K56" t="n">
+        <v>107.88</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="O56" t="n">
+        <v>268.7</v>
+      </c>
+      <c r="P56" t="n">
+        <v>345.4</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>422.2</v>
+      </c>
+      <c r="R56" t="n">
+        <v>498.9</v>
+      </c>
+      <c r="S56" t="n">
+        <v>575.7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>32</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="F57" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="G57" t="n">
+        <v>83</v>
+      </c>
+      <c r="H57" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="K57" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="P57" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>42</v>
+      </c>
+      <c r="R57" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="S57" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2420</v>
+      </c>
+      <c r="D58" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="E58" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="F58" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="G58" t="n">
+        <v>84</v>
+      </c>
+      <c r="H58" t="n">
+        <v>713.4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>239.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="K58" t="n">
+        <v>59.89</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>610.6</v>
+      </c>
+      <c r="O58" t="n">
+        <v>854.8</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1099.1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1343.3</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1587.6</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1831.8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>831</v>
+      </c>
+      <c r="D59" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="E59" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="G59" t="n">
+        <v>84</v>
+      </c>
+      <c r="H59" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="I59" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="J59" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>106.06</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="O59" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="P59" t="n">
+        <v>261.9</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>320.1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="S59" t="n">
+        <v>436.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>138</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="E60" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="F60" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="G60" t="n">
+        <v>84</v>
+      </c>
+      <c r="H60" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I60" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="K60" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="O60" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="P60" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="R60" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="S60" t="n">
+        <v>173.4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5312</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>寶島科</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="G61" t="n">
+        <v>84</v>
+      </c>
+      <c r="H61" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="I61" t="n">
+        <v>29</v>
+      </c>
+      <c r="J61" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="K61" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="L61" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="O61" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="P61" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="R61" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>176.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="E62" t="n">
+        <v>310.86</v>
+      </c>
+      <c r="F62" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="G62" t="n">
+        <v>85</v>
+      </c>
+      <c r="H62" t="n">
+        <v>249.4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>852.1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1322.58</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="O62" t="n">
+        <v>107</v>
+      </c>
+      <c r="P62" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="S62" t="n">
+        <v>229.2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2085</v>
+      </c>
+      <c r="D63" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="E63" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="F63" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="G63" t="n">
+        <v>86</v>
+      </c>
+      <c r="H63" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="I63" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="K63" t="n">
+        <v>184.21</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>270.4</v>
+      </c>
+      <c r="O63" t="n">
+        <v>378.6</v>
+      </c>
+      <c r="P63" t="n">
+        <v>486.7</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>594.9</v>
+      </c>
+      <c r="R63" t="n">
+        <v>703</v>
+      </c>
+      <c r="S63" t="n">
+        <v>811.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>6776</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>展碁國際</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E64" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="F64" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>87</v>
+      </c>
+      <c r="H64" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="I64" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="J64" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="K64" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L64" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="O64" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="P64" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="R64" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S64" t="n">
+        <v>129.9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>集雅社</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="E65" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="G65" t="n">
+        <v>89</v>
+      </c>
+      <c r="H65" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="I65" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="J65" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="K65" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="L65" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="P65" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="R65" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="S65" t="n">
+        <v>114.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>6788</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>華景電</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="E66" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="F66" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="G66" t="n">
+        <v>90</v>
+      </c>
+      <c r="H66" t="n">
+        <v>247</v>
+      </c>
+      <c r="I66" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="K66" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="O66" t="n">
+        <v>258.9</v>
+      </c>
+      <c r="P66" t="n">
+        <v>332.8</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>406.8</v>
+      </c>
+      <c r="R66" t="n">
+        <v>480.7</v>
+      </c>
+      <c r="S66" t="n">
+        <v>554.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1370</v>
+      </c>
+      <c r="D67" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="E67" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="F67" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="G67" t="n">
+        <v>90</v>
+      </c>
+      <c r="H67" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>289.1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="K67" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="O67" t="n">
+        <v>479.1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>616</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>752.8</v>
+      </c>
+      <c r="R67" t="n">
+        <v>889.7</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1026.6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>上詮</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>902</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E68" t="n">
+        <v>5637.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G68" t="n">
+        <v>90</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" t="n">
+        <v>44278.1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="K68" t="n">
+        <v>12233.33</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O68" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R68" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>茂達</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>394</v>
+      </c>
+      <c r="D69" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="E69" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="G69" t="n">
+        <v>91</v>
+      </c>
+      <c r="H69" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="I69" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="K69" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="O69" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="P69" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>310.6</v>
+      </c>
+      <c r="R69" t="n">
+        <v>367.1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>423.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E70" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="F70" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G70" t="n">
+        <v>92</v>
+      </c>
+      <c r="H70" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I70" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="K70" t="n">
+        <v>30</v>
+      </c>
+      <c r="L70" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>19</v>
+      </c>
+      <c r="O70" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="P70" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="R70" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="S70" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>毅嘉</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E71" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="F71" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="G71" t="n">
+        <v>92</v>
+      </c>
+      <c r="H71" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="I71" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="J71" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="K71" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O71" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="P71" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>51</v>
+      </c>
+      <c r="S71" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>三聯</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E72" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G72" t="n">
+        <v>94</v>
+      </c>
+      <c r="H72" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="J72" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="K72" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="O72" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="P72" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R72" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>123.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5278</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>尚凡*</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E73" t="n">
+        <v>25</v>
+      </c>
+      <c r="F73" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="G73" t="n">
+        <v>94</v>
+      </c>
+      <c r="H73" t="n">
+        <v>12</v>
+      </c>
+      <c r="I73" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K73" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="O73" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="P73" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R73" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="S73" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>矽創</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>315</v>
+      </c>
+      <c r="D74" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E74" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="F74" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G74" t="n">
+        <v>94</v>
+      </c>
+      <c r="H74" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="I74" t="n">
+        <v>172.9</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K74" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="L74" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>158</v>
+      </c>
+      <c r="O74" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="P74" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>347.6</v>
+      </c>
+      <c r="R74" t="n">
+        <v>410.8</v>
+      </c>
+      <c r="S74" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>波若威</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>870</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="E75" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>94</v>
+      </c>
+      <c r="H75" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="I75" t="n">
+        <v>632.1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="K75" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>121</v>
+      </c>
+      <c r="P75" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>224.6</v>
+      </c>
+      <c r="S75" t="n">
+        <v>259.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E76" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="F76" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="G76" t="n">
+        <v>95</v>
+      </c>
+      <c r="H76" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>76</v>
+      </c>
+      <c r="J76" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="K76" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="O76" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="R76" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>122.4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>世禾</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="D77" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="E77" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="F77" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="G77" t="n">
+        <v>95</v>
+      </c>
+      <c r="H77" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="I77" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="K77" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="O77" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="P77" t="n">
+        <v>156.4</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="R77" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="S77" t="n">
+        <v>260.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>108</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E78" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="F78" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="G78" t="n">
+        <v>95</v>
+      </c>
+      <c r="H78" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="K78" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="L78" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="O78" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="P78" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="R78" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="S78" t="n">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6612</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>奈米醫材</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E79" t="n">
+        <v>85.76000000000001</v>
+      </c>
+      <c r="F79" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="G79" t="n">
+        <v>96</v>
+      </c>
+      <c r="H79" t="n">
+        <v>27</v>
+      </c>
+      <c r="I79" t="n">
+        <v>170</v>
+      </c>
+      <c r="J79" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="K79" t="n">
+        <v>104.26</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="P79" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="R79" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>6683</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>雍智科技</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1605</v>
+      </c>
+      <c r="D80" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="E80" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="F80" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="G80" t="n">
+        <v>96</v>
+      </c>
+      <c r="H80" t="n">
+        <v>263.4</v>
+      </c>
+      <c r="I80" t="n">
+        <v>509.4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="K80" t="n">
+        <v>166.34</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="O80" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="P80" t="n">
+        <v>322</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>393.6</v>
+      </c>
+      <c r="R80" t="n">
+        <v>465.1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>536.7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>552</v>
+      </c>
+      <c r="D81" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="E81" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="F81" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="G81" t="n">
+        <v>96</v>
+      </c>
+      <c r="H81" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="I81" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="K81" t="n">
+        <v>132.23</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="P81" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="R81" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="S81" t="n">
+        <v>165.9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2150</v>
+      </c>
+      <c r="D82" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="E82" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="F82" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="G82" t="n">
+        <v>97</v>
+      </c>
+      <c r="H82" t="n">
+        <v>651.1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="J82" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="K82" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="P82" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="R82" t="n">
+        <v>704.9</v>
+      </c>
+      <c r="S82" t="n">
+        <v>813.3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>3840</v>
+      </c>
+      <c r="D83" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="E83" t="n">
+        <v>104.63</v>
+      </c>
+      <c r="F83" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="G83" t="n">
+        <v>97</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1135.5</v>
+      </c>
+      <c r="I83" t="n">
+        <v>238.2</v>
+      </c>
+      <c r="J83" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="K83" t="n">
+        <v>148.12</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>367</v>
+      </c>
+      <c r="O83" t="n">
+        <v>513.8</v>
+      </c>
+      <c r="P83" t="n">
+        <v>660.6</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>807.4</v>
+      </c>
+      <c r="R83" t="n">
+        <v>954.2</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>閎康</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>323</v>
+      </c>
+      <c r="D84" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="E84" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="F84" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>97</v>
+      </c>
+      <c r="H84" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I84" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="J84" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="K84" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="O84" t="n">
+        <v>106</v>
+      </c>
+      <c r="P84" t="n">
+        <v>136.3</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="R84" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="S84" t="n">
+        <v>227.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>意德士</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>293</v>
+      </c>
+      <c r="D85" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="E85" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="F85" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="G85" t="n">
+        <v>98</v>
+      </c>
+      <c r="H85" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="I85" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J85" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="K85" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="O85" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="P85" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>169</v>
+      </c>
+      <c r="R85" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="S85" t="n">
+        <v>230.4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1395</v>
+      </c>
+      <c r="D86" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="F86" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="G86" t="n">
+        <v>98</v>
+      </c>
+      <c r="H86" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="I86" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="K86" t="n">
+        <v>76.17</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>227</v>
+      </c>
+      <c r="O86" t="n">
+        <v>317.8</v>
+      </c>
+      <c r="P86" t="n">
+        <v>408.6</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>499.4</v>
+      </c>
+      <c r="R86" t="n">
+        <v>590.2</v>
+      </c>
+      <c r="S86" t="n">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E87" t="n">
+        <v>129.18</v>
+      </c>
+      <c r="F87" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>99</v>
+      </c>
+      <c r="H87" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="I87" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="K87" t="n">
+        <v>140.06</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="O87" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="P87" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="R87" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="S87" t="n">
+        <v>95.09999999999999</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>新產</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>143</v>
+      </c>
+      <c r="D88" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="E88" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="F88" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G88" t="n">
+        <v>99</v>
+      </c>
+      <c r="H88" t="n">
+        <v>88</v>
+      </c>
+      <c r="I88" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J88" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="K88" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L88" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="O88" t="n">
+        <v>171.9</v>
+      </c>
+      <c r="P88" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="R88" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="S88" t="n">
+        <v>368.4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2510</v>
+      </c>
+      <c r="D89" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="E89" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="F89" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="G89" t="n">
+        <v>99</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1167.3</v>
+      </c>
+      <c r="I89" t="n">
+        <v>115</v>
+      </c>
+      <c r="J89" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="K89" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>743.9</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1041.5</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1339</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1636.6</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1934.1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>2231.7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>辛耘</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>889</v>
+      </c>
+      <c r="D90" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="E90" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="F90" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="G90" t="n">
+        <v>99</v>
+      </c>
+      <c r="H90" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="I90" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="K90" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="O90" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="P90" t="n">
+        <v>265.7</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>324.7</v>
+      </c>
+      <c r="R90" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="S90" t="n">
+        <v>442.8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2595</v>
+      </c>
+      <c r="D91" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="E91" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="F91" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G91" t="n">
+        <v>99</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="J91" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="K91" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>528.8</v>
+      </c>
+      <c r="O91" t="n">
+        <v>740.3</v>
+      </c>
+      <c r="P91" t="n">
+        <v>951.8</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1163.4</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1374.9</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1586.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>19275</v>
+      </c>
+      <c r="D92" t="n">
+        <v>117.87</v>
+      </c>
+      <c r="E92" t="n">
+        <v>163.53</v>
+      </c>
+      <c r="F92" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="G92" t="n">
+        <v>99</v>
+      </c>
+      <c r="H92" t="n">
+        <v>5889.5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>227.3</v>
+      </c>
+      <c r="J92" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="K92" t="n">
+        <v>179.95</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>1178.7</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1650.2</v>
+      </c>
+      <c r="P92" t="n">
+        <v>2121.7</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2593.1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>3064.6</v>
+      </c>
+      <c r="S92" t="n">
+        <v>3536.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>7550</v>
+      </c>
+      <c r="D93" t="n">
+        <v>113.46</v>
+      </c>
+      <c r="E93" t="n">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="F93" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="G93" t="n">
         <v>100</v>
       </c>
-      <c r="H21" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>206.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="K21" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="P21" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="R21" t="n">
-        <v>121.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>140.1</v>
+      <c r="H93" t="n">
+        <v>1932.4</v>
+      </c>
+      <c r="I93" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="J93" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="K93" t="n">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1588.4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>2042.3</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>2496.1</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2950</v>
+      </c>
+      <c r="S93" t="n">
+        <v>3403.8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="D94" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E94" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="F94" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="G94" t="n">
+        <v>100</v>
+      </c>
+      <c r="H94" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>215.9</v>
+      </c>
+      <c r="J94" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="K94" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="L94" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>57</v>
+      </c>
+      <c r="O94" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="P94" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="R94" t="n">
+        <v>148.2</v>
+      </c>
+      <c r="S94" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>6425</v>
+      </c>
+      <c r="D95" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="E95" t="n">
+        <v>167.58</v>
+      </c>
+      <c r="F95" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>100</v>
+      </c>
+      <c r="H95" t="n">
+        <v>463.9</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1285</v>
+      </c>
+      <c r="J95" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="K95" t="n">
+        <v>187.82</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="O95" t="n">
+        <v>536.8</v>
+      </c>
+      <c r="P95" t="n">
+        <v>690.1</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>843.5</v>
+      </c>
+      <c r="R95" t="n">
+        <v>996.8</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1150.2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E96" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="G96" t="n">
+        <v>100</v>
+      </c>
+      <c r="H96" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I96" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="K96" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="L96" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="O96" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="P96" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="R96" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="S96" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>5825</v>
+      </c>
+      <c r="D97" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="E97" t="n">
+        <v>125.13</v>
+      </c>
+      <c r="F97" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G97" t="n">
+        <v>100</v>
+      </c>
+      <c r="H97" t="n">
+        <v>619.1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>840.9</v>
+      </c>
+      <c r="J97" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="K97" t="n">
+        <v>125.13</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="O97" t="n">
+        <v>651.7</v>
+      </c>
+      <c r="P97" t="n">
+        <v>837.9</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1024.1</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1210.3</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1396.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="E98" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F98" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G98" t="n">
+        <v>100</v>
+      </c>
+      <c r="H98" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="I98" t="n">
+        <v>283.3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="K98" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="O98" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="P98" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>147</v>
+      </c>
+      <c r="R98" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="S98" t="n">
+        <v>200.4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>6449</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>鈺邦</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="D99" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="E99" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F99" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G99" t="n">
+        <v>100</v>
+      </c>
+      <c r="H99" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="K99" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="O99" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="P99" t="n">
+        <v>143.1</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="R99" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="S99" t="n">
+        <v>238.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>566</v>
+      </c>
+      <c r="D100" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="E100" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="G100" t="n">
+        <v>100</v>
+      </c>
+      <c r="H100" t="n">
+        <v>200.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="J100" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K100" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="L100" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>205.8</v>
+      </c>
+      <c r="O100" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="P100" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>452.8</v>
+      </c>
+      <c r="R100" t="n">
+        <v>535.1</v>
+      </c>
+      <c r="S100" t="n">
+        <v>617.4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>6525</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>捷敏-KY</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>155</v>
+      </c>
+      <c r="D101" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="E101" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="F101" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="G101" t="n">
+        <v>100</v>
+      </c>
+      <c r="H101" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="I101" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="J101" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="K101" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="L101" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="O101" t="n">
+        <v>85</v>
+      </c>
+      <c r="P101" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="R101" t="n">
+        <v>157.8</v>
+      </c>
+      <c r="S101" t="n">
+        <v>182.1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D102" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="E102" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="F102" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="G102" t="n">
+        <v>100</v>
+      </c>
+      <c r="H102" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="I102" t="n">
+        <v>910.9</v>
+      </c>
+      <c r="J102" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="K102" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="O102" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="P102" t="n">
+        <v>253.1</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="R102" t="n">
+        <v>365.6</v>
+      </c>
+      <c r="S102" t="n">
+        <v>421.8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>3715</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>定穎投控</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="G103" t="n">
+        <v>100</v>
+      </c>
+      <c r="H103" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1277.7</v>
+      </c>
+      <c r="J103" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="K103" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>10</v>
+      </c>
+      <c r="O103" t="n">
+        <v>14</v>
+      </c>
+      <c r="P103" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>22</v>
+      </c>
+      <c r="R103" t="n">
+        <v>26</v>
+      </c>
+      <c r="S103" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/PE買入區間監看.xlsx
+++ b/data/PE買入區間監看.xlsx
@@ -565,7 +565,7 @@
         <v>1126.92</v>
       </c>
       <c r="L2" t="n">
-        <v>5.24</v>
+        <v>5.35</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>37.25</v>
       </c>
       <c r="L5" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>453.08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.77</v>
+        <v>3.88</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>89.78</v>
       </c>
       <c r="L11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>21.94</v>
       </c>
       <c r="L13" t="n">
-        <v>6.56</v>
+        <v>6.58</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>23.18</v>
       </c>
       <c r="L14" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>1126.92</v>
       </c>
       <c r="L2" t="n">
-        <v>5.24</v>
+        <v>5.35</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>37.25</v>
       </c>
       <c r="L5" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>453.08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.77</v>
+        <v>3.88</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>89.78</v>
       </c>
       <c r="L11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>21.94</v>
       </c>
       <c r="L13" t="n">
-        <v>6.56</v>
+        <v>6.58</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>23.18</v>
       </c>
       <c r="L14" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>26.18</v>
       </c>
       <c r="L18" t="n">
-        <v>6.42</v>
+        <v>6.32</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>23.95</v>
       </c>
       <c r="L21" t="n">
-        <v>5.3</v>
+        <v>5.32</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>29.17</v>
       </c>
       <c r="L22" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>179</v>
       </c>
       <c r="L28" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>51.42</v>
       </c>
       <c r="L29" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>31.47</v>
       </c>
       <c r="L31" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>36.11</v>
       </c>
       <c r="L33" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>16.01</v>
       </c>
       <c r="L35" t="n">
-        <v>5.35</v>
+        <v>5.39</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>510.49</v>
       </c>
       <c r="L36" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>36.15</v>
       </c>
       <c r="L39" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>29.13</v>
       </c>
       <c r="L40" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>64.83</v>
       </c>
       <c r="L41" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>40.44</v>
       </c>
       <c r="L47" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>89.53</v>
       </c>
       <c r="L48" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>111.49</v>
       </c>
       <c r="L49" t="n">
-        <v>5.32</v>
+        <v>5.33</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>5670</v>
       </c>
       <c r="L51" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>450</v>
       </c>
       <c r="L52" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>52.62</v>
       </c>
       <c r="L53" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>23.27</v>
       </c>
       <c r="L54" t="n">
-        <v>5.08</v>
+        <v>5.05</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>46.02</v>
       </c>
       <c r="L55" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>21.69</v>
       </c>
       <c r="L57" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>59.89</v>
       </c>
       <c r="L58" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>56.81</v>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>184.21</v>
       </c>
       <c r="L63" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>17.5</v>
       </c>
       <c r="L64" t="n">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>54.92</v>
       </c>
       <c r="L67" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>30</v>
       </c>
       <c r="L70" t="n">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>52.75</v>
       </c>
       <c r="L71" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>28.29</v>
       </c>
       <c r="L74" t="n">
-        <v>3.83</v>
+        <v>3.65</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>19.42</v>
       </c>
       <c r="L76" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>29.59</v>
       </c>
       <c r="L78" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>148.12</v>
       </c>
       <c r="L83" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>76.17</v>
       </c>
       <c r="L86" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>140.06</v>
       </c>
       <c r="L87" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>12.3</v>
       </c>
       <c r="L88" t="n">
-        <v>5.12</v>
+        <v>5.08</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>35.51</v>
       </c>
       <c r="L89" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>56.76</v>
       </c>
       <c r="L91" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>66.54000000000001</v>
       </c>
       <c r="L93" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>125.13</v>
       </c>
       <c r="L97" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>36.3</v>
       </c>
       <c r="L98" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>58.24</v>
       </c>
       <c r="L99" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>25.54</v>
       </c>
       <c r="L101" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>194.5</v>
       </c>
       <c r="L103" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
